--- a/Matriz_Implantacao_Catalogo_SEJUD.xlsx
+++ b/Matriz_Implantacao_Catalogo_SEJUD.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fdscosta\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A764EB55-6311-499A-99DC-11128304FA96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D96E6ECB-1BE2-4F3C-ADA7-0ADE51F54870}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="300" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resumo" sheetId="1" r:id="rId1"/>
@@ -966,13 +966,7 @@
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="tbCamposdosFormulrios" displayName="tbCamposdosFormulrios" ref="A1:I249">
-  <autoFilter ref="A1:I249" xr:uid="{00000000-0009-0000-0100-000002000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="SEJUD-029"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:I249" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Serviço"/>
@@ -3136,7 +3130,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>26</v>
       </c>
@@ -3165,7 +3159,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>26</v>
       </c>
@@ -3194,7 +3188,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>26</v>
       </c>
@@ -3223,7 +3217,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>26</v>
       </c>
@@ -3252,7 +3246,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>26</v>
       </c>
@@ -3281,7 +3275,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>26</v>
       </c>
@@ -3310,7 +3304,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>38</v>
       </c>
@@ -3339,7 +3333,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>38</v>
       </c>
@@ -3368,7 +3362,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>38</v>
       </c>
@@ -3397,7 +3391,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>38</v>
       </c>
@@ -3426,7 +3420,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>38</v>
       </c>
@@ -3455,7 +3449,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>38</v>
       </c>
@@ -3484,7 +3478,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>45</v>
       </c>
@@ -3513,7 +3507,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>45</v>
       </c>
@@ -3542,7 +3536,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>45</v>
       </c>
@@ -3571,7 +3565,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>45</v>
       </c>
@@ -3600,7 +3594,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>45</v>
       </c>
@@ -3629,7 +3623,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>45</v>
       </c>
@@ -3658,7 +3652,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>45</v>
       </c>
@@ -3687,7 +3681,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>53</v>
       </c>
@@ -3716,7 +3710,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>53</v>
       </c>
@@ -3745,7 +3739,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>53</v>
       </c>
@@ -3774,7 +3768,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>53</v>
       </c>
@@ -3803,7 +3797,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>53</v>
       </c>
@@ -3832,7 +3826,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>53</v>
       </c>
@@ -3861,7 +3855,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>53</v>
       </c>
@@ -3890,7 +3884,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>57</v>
       </c>
@@ -3919,7 +3913,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>57</v>
       </c>
@@ -3948,7 +3942,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>57</v>
       </c>
@@ -3977,7 +3971,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="31" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>57</v>
       </c>
@@ -4006,7 +4000,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>57</v>
       </c>
@@ -4035,7 +4029,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>57</v>
       </c>
@@ -4064,7 +4058,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>57</v>
       </c>
@@ -4093,7 +4087,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>64</v>
       </c>
@@ -4122,7 +4116,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>64</v>
       </c>
@@ -4151,7 +4145,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>64</v>
       </c>
@@ -4180,7 +4174,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
         <v>64</v>
       </c>
@@ -4209,7 +4203,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
         <v>64</v>
       </c>
@@ -4238,7 +4232,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
         <v>64</v>
       </c>
@@ -4267,7 +4261,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
         <v>64</v>
       </c>
@@ -4296,7 +4290,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
         <v>66</v>
       </c>
@@ -4325,7 +4319,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
         <v>66</v>
       </c>
@@ -4354,7 +4348,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
         <v>66</v>
       </c>
@@ -4383,7 +4377,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
         <v>66</v>
       </c>
@@ -4412,7 +4406,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
         <v>66</v>
       </c>
@@ -4441,7 +4435,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
         <v>66</v>
       </c>
@@ -4470,7 +4464,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
         <v>66</v>
       </c>
@@ -4499,7 +4493,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
         <v>71</v>
       </c>
@@ -4528,7 +4522,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
         <v>71</v>
       </c>
@@ -4557,7 +4551,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
         <v>71</v>
       </c>
@@ -4586,7 +4580,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
         <v>71</v>
       </c>
@@ -4615,7 +4609,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
         <v>71</v>
       </c>
@@ -4644,7 +4638,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
         <v>71</v>
       </c>
@@ -4673,7 +4667,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
         <v>71</v>
       </c>
@@ -4702,7 +4696,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
         <v>73</v>
       </c>
@@ -4731,7 +4725,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
         <v>73</v>
       </c>
@@ -4760,7 +4754,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
         <v>73</v>
       </c>
@@ -4789,7 +4783,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
         <v>73</v>
       </c>
@@ -4818,7 +4812,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
         <v>73</v>
       </c>
@@ -4847,7 +4841,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
         <v>73</v>
       </c>
@@ -4876,7 +4870,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
         <v>79</v>
       </c>
@@ -4905,7 +4899,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="63" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
         <v>79</v>
       </c>
@@ -4934,7 +4928,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
         <v>79</v>
       </c>
@@ -4963,7 +4957,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
         <v>79</v>
       </c>
@@ -4992,7 +4986,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
         <v>79</v>
       </c>
@@ -5021,7 +5015,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
         <v>79</v>
       </c>
@@ -5050,7 +5044,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
         <v>79</v>
       </c>
@@ -5079,7 +5073,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
         <v>85</v>
       </c>
@@ -5108,7 +5102,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
         <v>85</v>
       </c>
@@ -5137,7 +5131,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
         <v>85</v>
       </c>
@@ -5166,7 +5160,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="72" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
         <v>85</v>
       </c>
@@ -5195,7 +5189,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
         <v>85</v>
       </c>
@@ -5224,7 +5218,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="74" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
         <v>85</v>
       </c>
@@ -5253,7 +5247,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
         <v>85</v>
       </c>
@@ -5282,7 +5276,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
         <v>88</v>
       </c>
@@ -5311,7 +5305,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
         <v>88</v>
       </c>
@@ -5340,7 +5334,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
         <v>88</v>
       </c>
@@ -5369,7 +5363,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
         <v>88</v>
       </c>
@@ -5398,7 +5392,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="80" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
         <v>88</v>
       </c>
@@ -5427,7 +5421,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
         <v>88</v>
       </c>
@@ -5456,7 +5450,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="82" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
         <v>88</v>
       </c>
@@ -5485,7 +5479,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
         <v>93</v>
       </c>
@@ -5514,7 +5508,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="84" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
         <v>93</v>
       </c>
@@ -5543,7 +5537,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
         <v>93</v>
       </c>
@@ -5572,7 +5566,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
         <v>93</v>
       </c>
@@ -5601,7 +5595,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="87" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
         <v>93</v>
       </c>
@@ -5630,7 +5624,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
         <v>99</v>
       </c>
@@ -5659,7 +5653,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="89" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
         <v>99</v>
       </c>
@@ -5688,7 +5682,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="90" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
         <v>99</v>
       </c>
@@ -5717,7 +5711,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="91" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
         <v>99</v>
       </c>
@@ -5746,7 +5740,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="92" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
         <v>99</v>
       </c>
@@ -5775,7 +5769,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="93" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
         <v>99</v>
       </c>
@@ -5804,7 +5798,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="94" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
         <v>99</v>
       </c>
@@ -5833,7 +5827,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="95" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
         <v>99</v>
       </c>
@@ -5862,7 +5856,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="96" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
         <v>99</v>
       </c>
@@ -5891,7 +5885,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
         <v>106</v>
       </c>
@@ -5920,7 +5914,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="98" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
         <v>106</v>
       </c>
@@ -5949,7 +5943,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A99" s="4" t="s">
         <v>106</v>
       </c>
@@ -5978,7 +5972,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
         <v>106</v>
       </c>
@@ -6007,7 +6001,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
         <v>106</v>
       </c>
@@ -6036,7 +6030,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
         <v>106</v>
       </c>
@@ -6065,7 +6059,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="103" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A103" s="4" t="s">
         <v>106</v>
       </c>
@@ -6094,7 +6088,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="104" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
         <v>112</v>
       </c>
@@ -6123,7 +6117,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
         <v>112</v>
       </c>
@@ -6152,7 +6146,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
         <v>112</v>
       </c>
@@ -6181,7 +6175,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="4" t="s">
         <v>112</v>
       </c>
@@ -6210,7 +6204,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
         <v>112</v>
       </c>
@@ -6239,7 +6233,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="4" t="s">
         <v>112</v>
       </c>
@@ -6268,7 +6262,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
         <v>112</v>
       </c>
@@ -6297,7 +6291,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
         <v>112</v>
       </c>
@@ -6326,7 +6320,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="112" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
         <v>112</v>
       </c>
@@ -6355,7 +6349,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="113" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A113" s="4" t="s">
         <v>120</v>
       </c>
@@ -6384,7 +6378,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="114" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
         <v>120</v>
       </c>
@@ -6413,7 +6407,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="115" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A115" s="4" t="s">
         <v>120</v>
       </c>
@@ -6442,7 +6436,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="116" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
         <v>120</v>
       </c>
@@ -6471,7 +6465,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="117" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A117" s="4" t="s">
         <v>120</v>
       </c>
@@ -6500,7 +6494,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="118" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
         <v>120</v>
       </c>
@@ -6529,7 +6523,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="119" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A119" s="4" t="s">
         <v>120</v>
       </c>
@@ -6558,7 +6552,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="120" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
         <v>120</v>
       </c>
@@ -6587,7 +6581,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="121" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A121" s="4" t="s">
         <v>120</v>
       </c>
@@ -6616,7 +6610,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="122" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
         <v>122</v>
       </c>
@@ -6645,7 +6639,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="123" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A123" s="4" t="s">
         <v>122</v>
       </c>
@@ -6674,7 +6668,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="124" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
         <v>122</v>
       </c>
@@ -6703,7 +6697,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="125" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A125" s="4" t="s">
         <v>122</v>
       </c>
@@ -6732,7 +6726,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="126" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
         <v>122</v>
       </c>
@@ -6761,7 +6755,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="127" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A127" s="4" t="s">
         <v>122</v>
       </c>
@@ -6790,7 +6784,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="128" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
         <v>122</v>
       </c>
@@ -6819,7 +6813,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="129" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A129" s="4" t="s">
         <v>122</v>
       </c>
@@ -6848,7 +6842,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="130" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
         <v>122</v>
       </c>
@@ -6877,7 +6871,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="131" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A131" s="4" t="s">
         <v>128</v>
       </c>
@@ -6906,7 +6900,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="132" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
         <v>128</v>
       </c>
@@ -6935,7 +6929,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="133" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A133" s="4" t="s">
         <v>128</v>
       </c>
@@ -6964,7 +6958,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="134" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
         <v>128</v>
       </c>
@@ -6993,7 +6987,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="135" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A135" s="4" t="s">
         <v>128</v>
       </c>
@@ -7022,7 +7016,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="136" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
         <v>128</v>
       </c>
@@ -7051,7 +7045,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="137" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A137" s="4" t="s">
         <v>128</v>
       </c>
@@ -7080,7 +7074,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="138" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
         <v>128</v>
       </c>
@@ -7109,7 +7103,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="139" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A139" s="4" t="s">
         <v>128</v>
       </c>
@@ -7138,7 +7132,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="140" spans="1:9" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
         <v>130</v>
       </c>
@@ -7167,7 +7161,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="141" spans="1:9" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A141" s="4" t="s">
         <v>130</v>
       </c>
@@ -7196,7 +7190,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="142" spans="1:9" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
         <v>130</v>
       </c>
@@ -7225,7 +7219,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="143" spans="1:9" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A143" s="4" t="s">
         <v>130</v>
       </c>
@@ -7254,7 +7248,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="144" spans="1:9" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
         <v>130</v>
       </c>
@@ -7283,7 +7277,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="145" spans="1:9" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A145" s="4" t="s">
         <v>130</v>
       </c>
@@ -7312,7 +7306,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="146" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
         <v>136</v>
       </c>
@@ -7341,7 +7335,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="147" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A147" s="4" t="s">
         <v>136</v>
       </c>
@@ -7370,7 +7364,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="148" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
         <v>136</v>
       </c>
@@ -7399,7 +7393,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="149" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A149" s="4" t="s">
         <v>136</v>
       </c>
@@ -7428,7 +7422,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="150" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
         <v>136</v>
       </c>
@@ -7457,7 +7451,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="151" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A151" s="4" t="s">
         <v>136</v>
       </c>
@@ -7486,7 +7480,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="152" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
         <v>136</v>
       </c>
@@ -7515,7 +7509,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="153" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A153" s="4" t="s">
         <v>136</v>
       </c>
@@ -7544,7 +7538,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="154" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
         <v>136</v>
       </c>
@@ -7573,7 +7567,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="155" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A155" s="4" t="s">
         <v>142</v>
       </c>
@@ -7602,7 +7596,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="156" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
         <v>142</v>
       </c>
@@ -7631,7 +7625,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="157" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A157" s="4" t="s">
         <v>142</v>
       </c>
@@ -7660,7 +7654,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="158" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
         <v>142</v>
       </c>
@@ -7689,7 +7683,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="159" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A159" s="4" t="s">
         <v>142</v>
       </c>
@@ -7718,7 +7712,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="160" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
         <v>142</v>
       </c>
@@ -7747,7 +7741,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="161" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A161" s="4" t="s">
         <v>142</v>
       </c>
@@ -7776,7 +7770,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="162" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
         <v>142</v>
       </c>
@@ -7805,7 +7799,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="163" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A163" s="4" t="s">
         <v>142</v>
       </c>
@@ -7834,7 +7828,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="164" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
         <v>144</v>
       </c>
@@ -7863,7 +7857,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="165" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A165" s="4" t="s">
         <v>144</v>
       </c>
@@ -7892,7 +7886,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="166" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
         <v>144</v>
       </c>
@@ -7921,7 +7915,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="167" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A167" s="4" t="s">
         <v>144</v>
       </c>
@@ -7950,7 +7944,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="168" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
         <v>144</v>
       </c>
@@ -7979,7 +7973,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="169" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A169" s="4" t="s">
         <v>144</v>
       </c>
@@ -8008,7 +8002,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="170" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
         <v>144</v>
       </c>
@@ -8037,7 +8031,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="171" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A171" s="4" t="s">
         <v>144</v>
       </c>
@@ -8066,7 +8060,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="172" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
         <v>144</v>
       </c>
@@ -8095,7 +8089,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="173" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A173" s="4" t="s">
         <v>149</v>
       </c>
@@ -8124,7 +8118,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="174" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
         <v>149</v>
       </c>
@@ -8153,7 +8147,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="175" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A175" s="4" t="s">
         <v>149</v>
       </c>
@@ -8182,7 +8176,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="176" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
         <v>149</v>
       </c>
@@ -8211,7 +8205,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="177" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A177" s="4" t="s">
         <v>149</v>
       </c>
@@ -8240,7 +8234,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="178" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
         <v>149</v>
       </c>
@@ -8269,7 +8263,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="179" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A179" s="4" t="s">
         <v>149</v>
       </c>
@@ -8298,7 +8292,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="180" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
         <v>149</v>
       </c>
@@ -8327,7 +8321,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="181" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A181" s="4" t="s">
         <v>149</v>
       </c>
@@ -8356,7 +8350,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="182" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
         <v>151</v>
       </c>
@@ -8385,7 +8379,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="183" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A183" s="4" t="s">
         <v>151</v>
       </c>
@@ -8414,7 +8408,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="184" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
         <v>151</v>
       </c>
@@ -8443,7 +8437,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="185" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A185" s="4" t="s">
         <v>151</v>
       </c>
@@ -8472,7 +8466,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="186" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
         <v>151</v>
       </c>
@@ -8501,7 +8495,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="187" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A187" s="4" t="s">
         <v>151</v>
       </c>
@@ -8530,7 +8524,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="188" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
         <v>151</v>
       </c>
@@ -8559,7 +8553,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="189" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A189" s="4" t="s">
         <v>151</v>
       </c>
@@ -8588,7 +8582,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="190" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
         <v>151</v>
       </c>
@@ -8617,7 +8611,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="191" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A191" s="4" t="s">
         <v>157</v>
       </c>
@@ -8646,7 +8640,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="192" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
         <v>157</v>
       </c>
@@ -8675,7 +8669,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="193" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A193" s="4" t="s">
         <v>157</v>
       </c>
@@ -8704,7 +8698,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="194" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
         <v>157</v>
       </c>
@@ -8733,7 +8727,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="195" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A195" s="4" t="s">
         <v>157</v>
       </c>
@@ -8762,7 +8756,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="196" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
         <v>157</v>
       </c>
@@ -8791,7 +8785,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="197" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A197" s="4" t="s">
         <v>157</v>
       </c>
@@ -8820,7 +8814,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="198" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
         <v>157</v>
       </c>
@@ -8849,7 +8843,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="199" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A199" s="4" t="s">
         <v>157</v>
       </c>
@@ -8878,7 +8872,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="200" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
         <v>159</v>
       </c>
@@ -8907,7 +8901,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="201" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A201" s="4" t="s">
         <v>159</v>
       </c>
@@ -8936,7 +8930,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="202" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
         <v>159</v>
       </c>
@@ -8965,7 +8959,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="203" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A203" s="4" t="s">
         <v>159</v>
       </c>
@@ -8994,7 +8988,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="204" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
         <v>159</v>
       </c>
@@ -9023,7 +9017,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="205" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A205" s="4" t="s">
         <v>159</v>
       </c>
@@ -9052,7 +9046,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="206" spans="1:9" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A206" s="4" t="s">
         <v>159</v>
       </c>
@@ -9081,7 +9075,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="207" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A207" s="4" t="s">
         <v>166</v>
       </c>
@@ -9110,7 +9104,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="208" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A208" s="4" t="s">
         <v>166</v>
       </c>
@@ -9139,7 +9133,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="209" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A209" s="4" t="s">
         <v>166</v>
       </c>
@@ -9168,7 +9162,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="210" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A210" s="4" t="s">
         <v>166</v>
       </c>
@@ -9197,7 +9191,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="211" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A211" s="4" t="s">
         <v>166</v>
       </c>
@@ -9226,7 +9220,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="212" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A212" s="4" t="s">
         <v>166</v>
       </c>
@@ -9255,7 +9249,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="213" spans="1:9" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A213" s="4" t="s">
         <v>166</v>
       </c>
@@ -9545,7 +9539,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="223" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A223" s="4" t="s">
         <v>176</v>
       </c>
@@ -9574,7 +9568,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="224" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" s="4" t="s">
         <v>176</v>
       </c>
@@ -9603,7 +9597,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="225" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A225" s="4" t="s">
         <v>176</v>
       </c>
@@ -9632,7 +9626,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="226" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226" s="4" t="s">
         <v>176</v>
       </c>
@@ -9661,7 +9655,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="227" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227" s="4" t="s">
         <v>176</v>
       </c>
@@ -9690,7 +9684,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="228" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A228" s="4" t="s">
         <v>176</v>
       </c>
@@ -9719,7 +9713,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="229" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A229" s="4" t="s">
         <v>176</v>
       </c>
@@ -9748,7 +9742,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="230" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A230" s="4" t="s">
         <v>176</v>
       </c>
@@ -9777,7 +9771,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="231" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A231" s="4" t="s">
         <v>176</v>
       </c>
@@ -9806,7 +9800,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="232" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A232" s="4" t="s">
         <v>179</v>
       </c>
@@ -9835,7 +9829,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="233" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A233" s="4" t="s">
         <v>179</v>
       </c>
@@ -9864,7 +9858,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="234" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A234" s="4" t="s">
         <v>179</v>
       </c>
@@ -9893,7 +9887,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="235" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A235" s="4" t="s">
         <v>179</v>
       </c>
@@ -9922,7 +9916,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="236" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A236" s="4" t="s">
         <v>179</v>
       </c>
@@ -9951,7 +9945,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="237" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A237" s="4" t="s">
         <v>179</v>
       </c>
@@ -9980,7 +9974,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="238" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A238" s="4" t="s">
         <v>185</v>
       </c>
@@ -10009,7 +10003,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="239" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A239" s="4" t="s">
         <v>185</v>
       </c>
@@ -10038,7 +10032,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="240" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A240" s="4" t="s">
         <v>185</v>
       </c>
@@ -10067,7 +10061,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="241" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A241" s="4" t="s">
         <v>185</v>
       </c>
@@ -10096,7 +10090,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="242" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A242" s="4" t="s">
         <v>185</v>
       </c>
@@ -10125,7 +10119,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="243" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A243" s="4" t="s">
         <v>185</v>
       </c>
@@ -10154,7 +10148,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="244" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A244" s="4" t="s">
         <v>191</v>
       </c>
@@ -10183,7 +10177,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="245" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A245" s="4" t="s">
         <v>191</v>
       </c>
@@ -10212,7 +10206,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="246" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A246" s="4" t="s">
         <v>191</v>
       </c>
@@ -10241,7 +10235,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="247" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A247" s="4" t="s">
         <v>191</v>
       </c>
@@ -10270,7 +10264,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="248" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A248" s="4" t="s">
         <v>191</v>
       </c>
@@ -10299,7 +10293,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="249" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A249" s="4" t="s">
         <v>191</v>
       </c>
